--- a/医疗数据.xlsx
+++ b/医疗数据.xlsx
@@ -17,22 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,26 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,49 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>填写内容</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>填写数据</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>读取情况</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>当前身高</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>175cm</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/医疗数据.xlsx
+++ b/医疗数据.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +51,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,14 +436,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>填写内容</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>填写数据</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>数据原始依据</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>流程状态</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>完整度</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>解释</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>当前有无糖尿病</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Patient: 没有糖尿病</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>患者明确回答‘没有糖尿病’，符合字段要求中‘一般患者知道自己是否糖尿病’的判断前提，可直接确认为阴性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>（若无糖尿病）过去一年有无出现空腹血糖升高</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>AI: 过去一年里，有没有哪次体检或检查发现空腹血糖达到或超过7.0 mmol/L？/patient: 应该没有吧</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>患者在明确知晓问题含义（空腹血糖≥7.0mmol/L）后，以‘应该没有吧’表达否定倾向，属弱肯定式否定应答，在医疗随访语境中可合理解读为否认既往空腹血糖升高史，信息足以支持填表。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>是否曾患冠心病</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>AI: 您是否曾被医生诊断过冠心病？/Patient: 有曾经诊断出来过</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>患者明确回答'有曾经诊断出来过'，直接确认曾患冠心病，符合字段要求且信息充分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>（若曾患冠心病）是否为过去一年新发</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>AI: 那您是在2024年10月30日之后才第一次被诊断出冠心病的吗？/Patient: 什么意思</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>empty</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>患者对‘2024年10月30日之后才第一次被诊断出冠心病’这一时间界定表示不理解（‘什么意思’），说明其未明确回答‘是否为过去一年新发’，且当前提问方式存在歧义或时间表达不够直观，需换用更清晰表述重新询问。 已达到追问上限，先结束当前字段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>（若曾患冠心病）罹患冠心病至今时间</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1-2年</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>AI: 您被确诊冠心病大概有多久了？比如是最近一两年，还是更早一些？/Patient: 大概有一两年吧</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>患者明确回答‘大概有一两年吧’，符合字段要求中‘缺失提醒供者给出大概时间’的容错情形，可作为合理近似值填入；虽无精确起始日期，但‘一两年’已满足临床随访对病程粗略分层的需求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>（若曾患冠心病）治疗方式</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>阿司匹林，每日2-3片</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>AI: 那您确诊冠心病后，医生给您开了哪些药？比如阿司匹林、他汀这类，每天吃几次、每次几片？/Patient: 应该是阿司匹林有，一天吃两三片吧; AI: 那阿司匹林是每天吃几片？每片是多少毫克的？/Patient: 每天是吃两三片，应该差不多</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>患者明确提及‘阿司匹林’及‘每天吃两三片’，满足‘吃什么药、一天几次’的核心要求；但未说明单片剂量、是否联合其他药物、有无手术及治疗效果，故为部分完成；‘应该差不多’属模糊表达，但结合前序已确认用药种类和频次，信息已达可落表程度，按规则3优先收口。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>是否曾患脑血管病</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>AI: 请问您是否曾经罹患脑血管病？/Patient: 没</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>患者明确回答‘没’，符合字段要求中‘一般患者知道自己是否曾患脑血管病’，属清晰否定应答。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/医疗数据.xlsx
+++ b/医疗数据.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -479,17 +479,17 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>当前有无糖尿病</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>当前身高</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>169cm</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Patient: 没有糖尿病</t>
+          <t>Patient: 是169cm</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -504,194 +504,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>患者明确回答‘没有糖尿病’，符合字段要求中‘一般患者知道自己是否糖尿病’的判断前提，可直接确认为阴性。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>（若无糖尿病）过去一年有无出现空腹血糖升高</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>AI: 过去一年里，有没有哪次体检或检查发现空腹血糖达到或超过7.0 mmol/L？/patient: 应该没有吧</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>患者在明确知晓问题含义（空腹血糖≥7.0mmol/L）后，以‘应该没有吧’表达否定倾向，属弱肯定式否定应答，在医疗随访语境中可合理解读为否认既往空腹血糖升高史，信息足以支持填表。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>是否曾患冠心病</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>AI: 您是否曾被医生诊断过冠心病？/Patient: 有曾经诊断出来过</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>患者明确回答'有曾经诊断出来过'，直接确认曾患冠心病，符合字段要求且信息充分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>（若曾患冠心病）是否为过去一年新发</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>AI: 那您是在2024年10月30日之后才第一次被诊断出冠心病的吗？/Patient: 什么意思</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>empty</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>患者对‘2024年10月30日之后才第一次被诊断出冠心病’这一时间界定表示不理解（‘什么意思’），说明其未明确回答‘是否为过去一年新发’，且当前提问方式存在歧义或时间表达不够直观，需换用更清晰表述重新询问。 已达到追问上限，先结束当前字段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>（若曾患冠心病）罹患冠心病至今时间</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>1-2年</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>AI: 您被确诊冠心病大概有多久了？比如是最近一两年，还是更早一些？/Patient: 大概有一两年吧</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>患者明确回答‘大概有一两年吧’，符合字段要求中‘缺失提醒供者给出大概时间’的容错情形，可作为合理近似值填入；虽无精确起始日期，但‘一两年’已满足临床随访对病程粗略分层的需求。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>（若曾患冠心病）治疗方式</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>阿司匹林，每日2-3片</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>AI: 那您确诊冠心病后，医生给您开了哪些药？比如阿司匹林、他汀这类，每天吃几次、每次几片？/Patient: 应该是阿司匹林有，一天吃两三片吧; AI: 那阿司匹林是每天吃几片？每片是多少毫克的？/Patient: 每天是吃两三片，应该差不多</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>partial</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>患者明确提及‘阿司匹林’及‘每天吃两三片’，满足‘吃什么药、一天几次’的核心要求；但未说明单片剂量、是否联合其他药物、有无手术及治疗效果，故为部分完成；‘应该差不多’属模糊表达，但结合前序已确认用药种类和频次，信息已达可落表程度，按规则3优先收口。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>是否曾患脑血管病</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>AI: 请问您是否曾经罹患脑血管病？/Patient: 没</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>done</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>患者明确回答‘没’，符合字段要求中‘一般患者知道自己是否曾患脑血管病’，属清晰否定应答。</t>
+          <t>患者明确回答‘是169cm’，数值清晰、单位明确，符合身高字段最低可接受信息要求，可直接落表。 按身高字段规则收束。</t>
         </is>
       </c>
     </row>
